--- a/runs/RELX/2026-10-14/bear/scratch/g_tg_us_be/out/dcf.xlsx
+++ b/runs/RELX/2026-10-14/bear/scratch/g_tg_us_be/out/dcf.xlsx
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2044.926705519653</v>
+        <v>2102.881781249673</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.103145</v>
+        <v>0.0953618</v>
       </c>
     </row>
     <row r="18">
@@ -1420,7 +1420,7 @@
         <v/>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.09600960394000001</v>
+        <v>0.089224054516</v>
       </c>
     </row>
     <row r="20">
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>11133.7332424089</v>
+        <v>11302.6880463898</v>
       </c>
     </row>
     <row r="21">
@@ -1462,7 +1462,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>38749.35114985905</v>
+        <v>42737.81392426994</v>
       </c>
     </row>
     <row r="23">
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>25650.73511628922</v>
+        <v>29092.75146757816</v>
       </c>
     </row>
     <row r="24">
@@ -1490,7 +1490,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>36784.46835869812</v>
+        <v>40395.43951396796</v>
       </c>
     </row>
     <row r="25">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>29787.46835869812</v>
+        <v>33398.43951396796</v>
       </c>
     </row>
     <row r="27">
@@ -1532,7 +1532,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>28895.89141055117</v>
+        <v>32596.01908775804</v>
       </c>
     </row>
     <row r="28">
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>16.57107560090426</v>
+        <v>18.693006867908</v>
       </c>
     </row>
     <row r="29">
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1657.107560090426</v>
+        <v>1869.3006867908</v>
       </c>
     </row>
     <row r="30">
@@ -1574,7 +1574,7 @@
         <v/>
       </c>
       <c r="C30" s="6" t="n">
-        <v>-0.4019821147</v>
+        <v>-0.3254057428</v>
       </c>
     </row>
   </sheetData>
